--- a/src/test/resources/testData/APMT_Logins.xlsx
+++ b/src/test/resources/testData/APMT_Logins.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Channambika\HSI_Training\KODEXIQ\KodexIQAutomation\KodexIQAutomationFrameworkDevelopment\src\test\resources\testData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC030366-5C67-4DF8-BEAA-7C70AF736303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -19,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>username</t>
   </si>
@@ -64,16 +71,45 @@
   </si>
   <si>
     <t>Snipe@66</t>
+  </si>
+  <si>
+    <t>Super Admin</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>mallik@upl.com</t>
+  </si>
+  <si>
+    <t>ChangeMe@123</t>
+  </si>
+  <si>
+    <t>ram@infosys.com</t>
+  </si>
+  <si>
+    <t>tharun@infosys.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -96,14 +132,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -112,14 +150,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +198,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -229,7 +270,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -402,78 +443,144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D53E7DF-F015-4B48-981D-F7405A25AD7A}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3"/>
-    <hyperlink ref="B4" r:id="rId4"/>
-    <hyperlink ref="A5" r:id="rId5"/>
-    <hyperlink ref="B5" r:id="rId6"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{A8611002-FA17-4E54-A52F-8269D4CC6A32}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{8CEB8CB5-809A-4E8F-9B96-E3596E92B595}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{70F64E8F-E843-425F-9AB8-EF12CA60EA66}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{44981A8C-7335-442E-8467-6C99D387B4F8}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{E2757D23-820D-4625-8200-33296D96E850}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{35515912-8701-49DF-8244-81ED2B87870B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
